--- a/excel/QPD_Paper_Tables.xlsx
+++ b/excel/QPD_Paper_Tables.xlsx
@@ -97,7 +97,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -197,11 +197,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -272,6 +286,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -829,7 +861,7 @@
       <c r="R11" s="24" t="n"/>
       <c r="S11" s="23" t="inlineStr">
         <is>
-          <t>QFlex-T+ (not in paper)</t>
+          <t>QFlex-T+ (in the paper as Table A2)</t>
         </is>
       </c>
       <c r="T11" s="25" t="n"/>
@@ -1799,7 +1831,7 @@
       <c r="R28" s="24" t="n"/>
       <c r="S28" s="23" t="inlineStr">
         <is>
-          <t>QFlex-T+ (not in paper)</t>
+          <t>QFlex-T+ (in the paper as Table A2)</t>
         </is>
       </c>
       <c r="T28" s="25" t="n"/>
@@ -2740,7 +2772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3281,146 +3313,34 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n"/>
-      <c r="B24" s="22" t="n">
+      <c r="A24" s="28" t="n"/>
+      <c r="B24" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D24" s="8" t="n">
+      <c r="C24" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="D24" s="30" t="n">
         <v>0.34</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="31" t="n">
         <v>0.046</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="30" t="n">
         <v>2.73</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="4" t="n">
+      <c r="G24" s="33" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>QFlex-T+ (not in paper)</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="n"/>
-      <c r="B26" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="C26" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="G26" s="10" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="H26" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="n"/>
-      <c r="B27" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="n"/>
-      <c r="B28" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H28" s="10" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n"/>
+      <c r="A25" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3436,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3963,275 +3883,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="22" t="n">
+      <c r="A22" s="28" t="n"/>
+      <c r="B22" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="29" t="n">
         <v>88.8</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="29" t="n">
         <v>93</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="29" t="n">
         <v>6.8</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="30" t="n">
         <v>3.05</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>QFlex-T+ (not in paper)</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="11" t="n">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="11" t="n">
-        <v>5.56</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="n"/>
-      <c r="B25" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="C25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="11" t="n">
-        <v>4.54</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="n"/>
-      <c r="B26" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="C26" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="G26" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H26" s="11" t="n">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="n"/>
-      <c r="B27" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="C27" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H27" s="11" t="n">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="n"/>
-      <c r="B28" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="C28" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H28" s="11" t="n">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="n"/>
-      <c r="B29" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C29" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="H29" s="11" t="n">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="n"/>
-      <c r="B30" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="C30" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="H30" s="11" t="n">
-        <v>2.41</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="n"/>
-      <c r="B31" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="C31" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>73</v>
-      </c>
-      <c r="H31" s="11" t="n">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="n"/>
-      <c r="B32" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C32" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G32" s="10" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="H32" s="11" t="n">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n"/>
+      <c r="A23" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4244,7 +3920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4572,161 +4248,35 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>K = 13</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8" t="n">
+      <c r="B14" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="n">
         <v>0.28</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="31" t="n">
         <v>0.053</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="30" t="n">
         <v>3.13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Log QFlex-T+ (not in paper)</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>K = 4</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="H16" s="11" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>K = 7</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>K = 10</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="C18" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="H18" s="11" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>K = 13</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="H19" s="11" t="n">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Note: Validity percentages are calculated over all 1,000 bootstrap resamples. Mode-count percentages, interquartile ranges, and median W1 values are calculated over valid fits only. W1 measures the distance between each fitted quantile function and its corresponding bootstrap EQF.</t>
         </is>
@@ -4747,7 +4297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5587,256 +5137,260 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>K = 13</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C33" s="7" t="n">
+      <c r="B33" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="C33" s="29" t="n">
         <v>0.8</v>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="29" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="30" t="n">
         <v>0.31</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="31" t="n">
         <v>0.006</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="30" t="n">
         <v>0.14</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="H33" s="31" t="n">
         <v>0.008</v>
       </c>
-      <c r="I33" s="8" t="n">
+      <c r="I33" s="30" t="n">
         <v>0.91</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>Log QFlex-T+ (not in paper)</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="n"/>
-      <c r="C34" s="20" t="n"/>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="20" t="n"/>
-      <c r="F34" s="20" t="n"/>
-      <c r="G34" s="20" t="n"/>
-      <c r="H34" s="20" t="n"/>
-      <c r="I34" s="20" t="n"/>
-    </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>(Not in the paper.) Stability of model features for bootstrap fits to the fish weight data at 1.0 lb uniform jitter half-width. Secondary-mode IQRs are over the bimodal fits only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>QPD</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Validity %</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>1 mode %</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>2 modes %</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>Primary Mode IQR</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>Secondary Mode IQR</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>Median W1 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="n"/>
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>Location (lb)</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>Height (1/lb)</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>Location (lb)</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>Height (1/lb)</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Log Metalog</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="19" t="n"/>
+      <c r="H38" s="19" t="n"/>
+      <c r="I38" s="19" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>K = 4</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="11" t="n">
+      <c r="B39" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>K = 7</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>K = 10</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E41" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="F35" s="16" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>K = 7</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C36" s="10" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F36" s="16" t="n">
+      <c r="F41" s="13" t="n">
         <v>0.007</v>
       </c>
-      <c r="G36" s="11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H36" s="16" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I36" s="11" t="n">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>K = 10</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F37" s="16" t="n">
+      <c r="G41" s="8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>K = 13</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F42" s="13" t="n">
         <v>0.008</v>
       </c>
-      <c r="G37" s="11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H37" s="16" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="I37" s="11" t="n">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>K = 13</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="E38" s="11" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G38" s="11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H38" s="16" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>(Not in the paper.) Stability of model features for bootstrap fits to the fish weight data at 1.0 lb uniform jitter half-width. Secondary-mode IQRs are over the bimodal fits only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>QPD</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>Validity %</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>1 mode %</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
-        <is>
-          <t>2 modes %</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>Primary Mode IQR</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="n"/>
-      <c r="G41" s="23" t="inlineStr">
-        <is>
-          <t>Secondary Mode IQR</t>
-        </is>
-      </c>
-      <c r="H41" s="24" t="n"/>
-      <c r="I41" s="23" t="inlineStr">
-        <is>
-          <t>Median W1 (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="23" t="n"/>
-      <c r="B42" s="23" t="n"/>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="23" t="n"/>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>Location (lb)</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>Height (1/lb)</t>
-        </is>
-      </c>
-      <c r="G42" s="23" t="inlineStr">
-        <is>
-          <t>Location (lb)</t>
-        </is>
-      </c>
-      <c r="H42" s="23" t="inlineStr">
-        <is>
-          <t>Height (1/lb)</t>
-        </is>
-      </c>
-      <c r="I42" s="23" t="n"/>
+      <c r="G42" s="8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>Log Metalog</t>
+          <t>Log QFlex-TA+</t>
         </is>
       </c>
       <c r="B43" s="19" t="n"/>
@@ -5864,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="F44" s="13" t="n">
         <v>0.002</v>
@@ -5880,7 +5434,7 @@
         </is>
       </c>
       <c r="I44" s="8" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="45">
@@ -5899,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="F45" s="13" t="n">
         <v>0.006</v>
@@ -5915,7 +5469,7 @@
         </is>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.73</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="46">
@@ -5928,25 +5482,25 @@
         <v>100</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>71.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>28.3</v>
+        <v>5.6</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.45</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="47">
@@ -5959,31 +5513,31 @@
         <v>100</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>28.2</v>
+        <v>49.2</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>71.8</v>
+        <v>50.8</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>0.34</v>
+        <v>0.19</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.41</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>Log QFlex-TA+</t>
+          <t>Log QFlex-U</t>
         </is>
       </c>
       <c r="B48" s="19" t="n"/>
@@ -6062,7 +5616,7 @@
         </is>
       </c>
       <c r="I50" s="8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="51">
@@ -6075,141 +5629,95 @@
         <v>100</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>94.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F51" s="13" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>K = 13</t>
+        </is>
+      </c>
+      <c r="B52" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="C52" s="29" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D52" s="29" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="E52" s="30" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F52" s="31" t="n">
         <v>0.006</v>
       </c>
-      <c r="G51" s="8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H51" s="13" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I51" s="8" t="n">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>K = 13</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F52" s="13" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G52" s="8" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H52" s="13" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="I52" s="8" t="n">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>Log QFlex-U</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="n"/>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="19" t="n"/>
-      <c r="E53" s="19" t="n"/>
-      <c r="F53" s="19" t="n"/>
-      <c r="G53" s="19" t="n"/>
-      <c r="H53" s="19" t="n"/>
-      <c r="I53" s="19" t="n"/>
+      <c r="G52" s="30" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H52" s="31" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I52" s="30" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>K = 4</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G54" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v>2.7</v>
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>Table 11. Sensitivity of 10-Term and 13-Term Log Metalog Validity and Modality to Model Order and Sample Size</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>K = 7</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F55" s="13" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G55" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="8" t="n">
-        <v>1.03</v>
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>Log Metalog Order</t>
+        </is>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>Resamples (N)</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>Validity %</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>1 mode %</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>2 modes %</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>&gt; 2 modes %</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -6218,442 +5726,194 @@
           <t>K = 10</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
-        <v>100</v>
+      <c r="B56" s="22" t="n">
+        <v>200</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>94.90000000000001</v>
+        <v>55.4</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F56" s="13" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="G56" s="8" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H56" s="13" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="I56" s="8" t="n">
-        <v>0.64</v>
+        <v>18</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="3" t="n"/>
+      <c r="B57" s="22" t="n">
+        <v>400</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n"/>
+      <c r="B58" s="22" t="n">
+        <v>800</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n"/>
+      <c r="B59" s="22" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n"/>
+      <c r="B60" s="22" t="n">
+        <v>3474</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>K = 13</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C57" s="7" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="F57" s="13" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G57" s="8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H57" s="13" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I57" s="8" t="n">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>Log QFlex-T+ (not in paper)</t>
-        </is>
-      </c>
-      <c r="B58" s="20" t="n"/>
-      <c r="C58" s="20" t="n"/>
-      <c r="D58" s="20" t="n"/>
-      <c r="E58" s="20" t="n"/>
-      <c r="F58" s="20" t="n"/>
-      <c r="G58" s="20" t="n"/>
-      <c r="H58" s="20" t="n"/>
-      <c r="I58" s="20" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>K = 4</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C59" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D59" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="11" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F59" s="16" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I59" s="11" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>K = 7</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C60" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D60" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F60" s="16" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="n">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t>K = 10</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C61" s="10" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="D61" s="10" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E61" s="11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F61" s="16" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="G61" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H61" s="16" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I61" s="11" t="n">
-        <v>0.67</v>
+      <c r="B61" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>60.7</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>K = 13</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C62" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="D62" s="10" t="n">
-        <v>73</v>
-      </c>
-      <c r="E62" s="11" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F62" s="16" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G62" s="11" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H62" s="16" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I62" s="11" t="n">
-        <v>0.47</v>
+      <c r="A62" s="3" t="n"/>
+      <c r="B62" s="22" t="n">
+        <v>400</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n"/>
+      <c r="B63" s="22" t="n">
+        <v>800</v>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>7.3</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>Table 11. Sensitivity of 10-Term and 13-Term Log Metalog Validity and Modality to Model Order and Sample Size</t>
-        </is>
+      <c r="A64" s="3" t="n"/>
+      <c r="B64" s="22" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="23" t="inlineStr">
-        <is>
-          <t>Log Metalog Order</t>
-        </is>
-      </c>
-      <c r="B65" s="23" t="inlineStr">
-        <is>
-          <t>Resamples (N)</t>
-        </is>
-      </c>
-      <c r="C65" s="23" t="inlineStr">
-        <is>
-          <t>Validity %</t>
-        </is>
-      </c>
-      <c r="D65" s="23" t="inlineStr">
-        <is>
-          <t>1 mode %</t>
-        </is>
-      </c>
-      <c r="E65" s="23" t="inlineStr">
-        <is>
-          <t>2 modes %</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="inlineStr">
-        <is>
-          <t>&gt; 2 modes %</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>K = 10</t>
-        </is>
-      </c>
-      <c r="B66" s="22" t="n">
-        <v>200</v>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="D66" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="n"/>
-      <c r="B67" s="22" t="n">
-        <v>400</v>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="D67" s="7" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E67" s="7" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="F67" s="7" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="n"/>
-      <c r="B68" s="22" t="n">
-        <v>800</v>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="F68" s="7" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n"/>
-      <c r="B69" s="22" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C69" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="D69" s="7" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="E69" s="7" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="F69" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n"/>
-      <c r="B70" s="22" t="n">
+      <c r="A65" s="3" t="n"/>
+      <c r="B65" s="22" t="n">
         <v>3474</v>
       </c>
-      <c r="C70" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D70" s="7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E70" s="7" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>K = 13</t>
-        </is>
-      </c>
-      <c r="B71" s="22" t="n">
-        <v>200</v>
-      </c>
-      <c r="C71" s="7" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="D71" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E71" s="7" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F71" s="7" t="n">
-        <v>60.7</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="n"/>
-      <c r="B72" s="22" t="n">
-        <v>400</v>
-      </c>
-      <c r="C72" s="7" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="D72" s="7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E72" s="7" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="F72" s="7" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n"/>
-      <c r="B73" s="22" t="n">
-        <v>800</v>
-      </c>
-      <c r="C73" s="7" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="D73" s="7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="F73" s="7" t="n">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="n"/>
-      <c r="B74" s="22" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C74" s="7" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="D74" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E74" s="7" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="F74" s="7" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="n"/>
-      <c r="B75" s="22" t="n">
-        <v>3474</v>
-      </c>
-      <c r="C75" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D75" s="7" t="n">
+      <c r="C65" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D65" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="E75" s="7" t="n">
+      <c r="E65" s="7" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="F75" s="7" t="n">
+      <c r="F65" s="7" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="E41:F41"/>
     <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G36:H36"/>
     <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="E36:F36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6665,7 +5925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7540,378 +6800,40 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n"/>
-      <c r="B36" s="22" t="n">
+      <c r="A36" s="28" t="n"/>
+      <c r="B36" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="29" t="n">
         <v>92</v>
       </c>
-      <c r="D36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7" t="n">
+      <c r="D36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="29" t="n">
         <v>99.2</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="29" t="n">
         <v>0.8</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="30" t="n">
         <v>1.43</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="H36" s="31" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="I36" s="8" t="n">
+      <c r="I36" s="30" t="n">
         <v>0.73</v>
       </c>
-      <c r="J36" s="13" t="n">
+      <c r="J36" s="31" t="n">
         <v>0.048</v>
       </c>
-      <c r="K36" s="8" t="n">
+      <c r="K36" s="30" t="n">
         <v>1.8</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Log QFlex-T+ (not in paper)</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="11" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="H37" s="16" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K37" s="11" t="n">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="11" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H38" s="16" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="J38" s="16" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K38" s="11" t="n">
-        <v>4.66</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="n"/>
-      <c r="B39" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="11" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H39" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="J39" s="16" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K39" s="11" t="n">
-        <v>4.68</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G40" s="11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="H40" s="16" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="I40" s="11" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="J40" s="16" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="K40" s="11" t="n">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="n"/>
-      <c r="B41" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="F41" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G41" s="11" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="H41" s="16" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J41" s="16" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="K41" s="11" t="n">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="n"/>
-      <c r="B42" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="C42" s="10" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G42" s="11" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="H42" s="16" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="I42" s="11" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J42" s="16" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="K42" s="11" t="n">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="n"/>
-      <c r="B43" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="G43" s="11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H43" s="16" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="J43" s="16" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="K43" s="11" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="n"/>
-      <c r="B44" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="C44" s="10" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="G44" s="11" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="H44" s="16" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="I44" s="11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="J44" s="16" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="K44" s="11" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="n"/>
-      <c r="B45" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="C45" s="10" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="G45" s="11" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="H45" s="16" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="J45" s="16" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K45" s="11" t="n">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="n"/>
-      <c r="B46" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C46" s="10" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="G46" s="11" t="n">
-        <v>12.46</v>
-      </c>
-      <c r="H46" s="16" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="I46" s="11" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="J46" s="16" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K46" s="11" t="n">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Primary mode = the mode at the longer waiting time; secondary = the shorter. Secondary-mode IQRs are over fits with two or more modes.</t>
         </is>
@@ -7932,7 +6854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7962,7 +6884,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table O2. QPD fit summary for Monte Carlo realizations of the inverse Gaussian distribution (μ = 0.919, λ = 1.069).</t>
+          <t>Table O2. QPD fit summary for Monte Carlo realizations of the inverse Gaussian distribution (μ = 0.919, λ = 1.069), N = 200.</t>
         </is>
       </c>
     </row>
@@ -8323,362 +7245,96 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="22" t="n">
+      <c r="A7" s="28" t="n"/>
+      <c r="B7" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="29" t="n">
         <v>35.5</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="29" t="n">
         <v>83.7</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="30" t="n">
         <v>1.25</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="30" t="n">
         <v>1.15</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="29" t="n">
         <v>21.8</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="29" t="n">
         <v>89</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="30" t="n">
         <v>1.28</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="30" t="n">
         <v>1.12</v>
       </c>
-      <c r="K7" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="L7" s="7" t="n">
+      <c r="K7" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="L7" s="29" t="n">
         <v>29.1</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="30" t="n">
         <v>1.08</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="30" t="n">
         <v>1.54</v>
       </c>
-      <c r="O7" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="P7" s="7" t="n">
+      <c r="O7" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" s="29" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="30" t="n">
         <v>1.7</v>
       </c>
-      <c r="S7" s="7" t="n">
+      <c r="S7" s="29" t="n">
         <v>38.3</v>
       </c>
-      <c r="T7" s="7" t="n">
+      <c r="T7" s="29" t="n">
         <v>86.7</v>
       </c>
-      <c r="U7" s="8" t="n">
+      <c r="U7" s="30" t="n">
         <v>1.25</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="30" t="n">
         <v>1.13</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="B8" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="R8" s="8" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="S8" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>3.41</v>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="L9" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N9" s="8" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O9" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="P9" s="7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q9" s="8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="R9" s="8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S9" s="7" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="T9" s="7" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v>2.53</v>
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Same design as Johnson SL (Tables 4 and A1): 1000 replicates per N; Log transform with the true lower bound 0; the evaluation framework of Section 3.</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O10" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="P10" s="7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="S10" s="7" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="T10" s="7" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v>1.82</v>
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>IG parameters chosen to match Johnson SL at P10 / P50 / P90. True mode height = 1.1210 (mode at x = 0.3146).</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O11" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="P11" s="7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S11" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T11" s="7" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>Same design as Johnson SL (Tables 4 and A1): 1000 replicates per N; Log transform with the true lower bound 0; the evaluation framework of Section 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>IG parameters chosen to match Johnson SL at P10 / P50 / P90. True mode height = 1.1210 (mode at x = 0.3146).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>False Modality % and Mode Height are over valid fits; Median W1 is Equation 6, in % of the sample P90 - P10.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>Source: QPD_Overfitting_Repro/reproduction/tables/invgauss/mc_perrep_ig_n{200,50}.csv (scripts/mc_invgauss.py).</t>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Source: reproduction/tables/invgauss/TableO2_invgauss_n200.csv, from mc_perrep_ig_n200.csv (scripts/mc_invgauss.py, scripts/invgauss_table_O2.py).</t>
         </is>
       </c>
     </row>
